--- a/Main bearing/02. 자료/260703 유니슨 극한하중/EX.20260701.K26.DE.MainBearing_DesignLoads-A.xlsx
+++ b/Main bearing/02. 자료/260703 유니슨 극한하중/EX.20260701.K26.DE.MainBearing_DesignLoads-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KIMM\1. Project\01. 진행 프로젝트\10. 풍력발전기 메인베어링\03. 연구자료\01. Docs\04. 정리자료\2026년\TRB 최적설계\02. 본 설계\01. 하중데이터\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\AI_Seminar\Main bearing\02. 자료\260703 유니슨 극한하중\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4178623-CD8E-419E-8AD0-CA96750FA645}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2810033A-0493-4F1B-8F85-2B689E2BE3F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15700" windowHeight="10360" activeTab="3" xr2:uid="{3D30DDC3-562F-4DD7-BF29-1B7C3F7FAA1A}"/>
   </bookViews>
@@ -241,7 +241,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">- 두산 3MW 레포트와 본 자료를 검토했을 때, 극한 하중은 전체 로드케이스 중 각 힘/모멘트의 최대값이 나오는 17개의 케이스로 선정한다는 것을 확인
+      <t xml:space="preserve">- 두산 3MW 레포트와 본 자료를 검토했을 때, 극한 하중은 전체 로드케이스 중 각 힘/모멘트의 최대값이 나오는 16개의 케이스로 선정한다는 것을 확인
 </t>
     </r>
     <r>
@@ -1141,6 +1141,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1200,39 +1233,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1967,113 +1967,113 @@
   <sheetData>
     <row r="1" spans="3:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="3:11" x14ac:dyDescent="0.45">
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="51"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="3" spans="3:11" x14ac:dyDescent="0.45">
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="54"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
     </row>
     <row r="4" spans="3:11" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="70"/>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.45">
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="54"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="65"/>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.45">
-      <c r="C6" s="52"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="54"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="3:11" ht="30" x14ac:dyDescent="0.45">
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="62"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="73"/>
     </row>
     <row r="8" spans="3:11" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="59"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="70"/>
     </row>
     <row r="9" spans="3:11" ht="23" x14ac:dyDescent="0.45">
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="66"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="77"/>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.45">
-      <c r="C10" s="52"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="54"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="65"/>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C11" s="10"/>
@@ -2161,10 +2161,10 @@
       <c r="H25" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="47">
+      <c r="I25" s="58">
         <v>46204</v>
       </c>
-      <c r="J25" s="48"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.45">
@@ -2176,10 +2176,10 @@
       <c r="H26" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="48" t="s">
+      <c r="I26" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="48"/>
+      <c r="J26" s="59"/>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="3:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2195,62 +2195,62 @@
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C28" s="2"/>
-      <c r="D28" s="55" t="s">
+      <c r="D28" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="71" t="s">
+      <c r="E28" s="67"/>
+      <c r="F28" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="73"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C29" s="2"/>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="68"/>
-      <c r="F29" s="74" t="s">
+      <c r="E29" s="48"/>
+      <c r="F29" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="75"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="55"/>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C30" s="2"/>
-      <c r="D30" s="67" t="s">
+      <c r="D30" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="74" t="s">
+      <c r="E30" s="48"/>
+      <c r="F30" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="75"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="55"/>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="3:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C31" s="2"/>
-      <c r="D31" s="69" t="s">
+      <c r="D31" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="76" t="s">
+      <c r="E31" s="50"/>
+      <c r="F31" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="77"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="57"/>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.45">
@@ -2281,13 +2281,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="F29:J29"/>
-    <mergeCell ref="F30:J30"/>
-    <mergeCell ref="F31:J31"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="C2:K2"/>
@@ -2300,6 +2293,13 @@
     <mergeCell ref="C7:K7"/>
     <mergeCell ref="C8:K8"/>
     <mergeCell ref="C9:K9"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="F31:J31"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
